--- a/Grupo/RUC_Grupo.xlsx
+++ b/Grupo/RUC_Grupo.xlsx
@@ -458,16 +458,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>41.29659777219353</v>
+        <v>41.29659777219354</v>
       </c>
       <c r="C2" s="2">
-        <v>115.2363329361691</v>
+        <v>115.2177634832716</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>47.58868490007551</v>
+        <v>47.58101634780395</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -475,10 +475,10 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>1.042507049423838</v>
+        <v>1.042507049423837</v>
       </c>
       <c r="C3" s="2">
-        <v>114.0707222709756</v>
+        <v>114.0707222709757</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>6</v>
@@ -492,16 +492,16 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>4.767484993164734</v>
+        <v>4.767484993164736</v>
       </c>
       <c r="C4" s="2">
-        <v>104.6885634245338</v>
+        <v>104.6885634245337</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2">
-        <v>4.991011550824393</v>
+        <v>4.991011550824392</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -563,13 +563,13 @@
         <v>2.232383116905052</v>
       </c>
       <c r="C8" s="2">
-        <v>109.215843865456</v>
+        <v>109.2158438654559</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E8" s="2">
-        <v>2.438116059437821</v>
+        <v>2.43811605943782</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -611,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="2">
-        <v>5.943255309450393</v>
+        <v>5.943255309450394</v>
       </c>
       <c r="C11" s="2">
         <v>131.8361064518991</v>
